--- a/draft/FINAL_ENGINEER_CLIENTS_COMPLETE.xlsx
+++ b/draft/FINAL_ENGINEER_CLIENTS_COMPLETE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,10 +497,8 @@
           <t>Nyambura Mutonya</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>254715885492</t>
-        </is>
+      <c r="D2" t="n">
+        <v>254715885492</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -542,10 +540,8 @@
           <t>Wanjiku Nyaguthii</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>254716872853</t>
-        </is>
+      <c r="D3" t="n">
+        <v>254716872853</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -593,10 +589,8 @@
           <t>Wambui Mwangi</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>254713404733</t>
-        </is>
+      <c r="D4" t="n">
+        <v>254713404733</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -644,10 +638,8 @@
           <t>Bahati Bevlyne</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>254711670920</t>
-        </is>
+      <c r="D5" t="n">
+        <v>254711670920</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -695,10 +687,8 @@
           <t>Gichemba Noah</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>254746130036</t>
-        </is>
+      <c r="D6" t="n">
+        <v>254746130036</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -740,10 +730,8 @@
           <t>Wanjiku Gitonga</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>254725714984</t>
-        </is>
+      <c r="D7" t="n">
+        <v>254725714984</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -791,10 +779,8 @@
           <t>Kahura Kabiro</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>254725940977</t>
-        </is>
+      <c r="D8" t="n">
+        <v>254725940977</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -804,7 +790,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Isaac Njogu Muiruri</t>
@@ -838,10 +828,8 @@
           <t>Kariuki Wangaru</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>254741724262</t>
-        </is>
+      <c r="D9" t="n">
+        <v>254741724262</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -851,7 +839,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Michael Ndungu Kimani</t>
@@ -885,10 +877,8 @@
           <t>Waweru Wang'ombe</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>254721179725</t>
-        </is>
+      <c r="D10" t="n">
+        <v>254721179725</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -898,7 +888,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Isaac Kangau Muthee</t>
@@ -932,10 +926,8 @@
           <t>Wanjiru Mbae</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>254706414682</t>
-        </is>
+      <c r="D11" t="n">
+        <v>254706414682</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -945,7 +937,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>John Mbae Kimani</t>
@@ -979,10 +975,8 @@
           <t>Atieno Ochieng</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>254706200790</t>
-        </is>
+      <c r="D12" t="n">
+        <v>254706200790</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -992,7 +986,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Beatrice Akinyi Ombija</t>
@@ -1026,10 +1024,8 @@
           <t>Njeri Wanjiku</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>254119675041</t>
-        </is>
+      <c r="D13" t="n">
+        <v>254119675041</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -1039,7 +1035,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Ann Njoki Njanja</t>
@@ -1073,10 +1073,8 @@
           <t>Wanjiku Mwangi</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>254715072434</t>
-        </is>
+      <c r="D14" t="n">
+        <v>254715072434</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -1086,7 +1084,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Philip Muriithi Mwangi</t>
@@ -1120,10 +1122,8 @@
           <t>Wanjiru Kanyi</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>254729296712</t>
-        </is>
+      <c r="D15" t="n">
+        <v>254729296712</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -1133,7 +1133,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Eneta Wambui Mwaniki</t>
@@ -1167,10 +1171,8 @@
           <t>Kinyanjui Nguhi</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>254741304619</t>
-        </is>
+      <c r="D16" t="n">
+        <v>254741304619</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1180,7 +1182,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Isaac Mbae Nyoro</t>
@@ -1214,10 +1220,8 @@
           <t>Mugure Mwaura</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>254713068523</t>
-        </is>
+      <c r="D17" t="n">
+        <v>254713068523</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -1227,7 +1231,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Agnes Wambui Kamau</t>
@@ -1261,10 +1269,8 @@
           <t>Musyoka Kamene</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>254707420132</t>
-        </is>
+      <c r="D18" t="n">
+        <v>254707420132</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -1274,7 +1280,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Ann Wambui Nyambura</t>
@@ -1308,10 +1318,8 @@
           <t>Muthoni Wanjiru</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>254795042054</t>
-        </is>
+      <c r="D19" t="n">
+        <v>254795042054</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1321,7 +1329,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Pauline Ngubia Waweru</t>
@@ -1355,10 +1367,8 @@
           <t>Moraa Kirera</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>254728843845</t>
-        </is>
+      <c r="D20" t="n">
+        <v>254728843845</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1368,7 +1378,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Margaret Mwithaki Kimani</t>
@@ -1402,10 +1416,8 @@
           <t>Wanja Mwangi</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>254721422565</t>
-        </is>
+      <c r="D21" t="n">
+        <v>254721422565</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1415,7 +1427,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Catherine Njeri Monyo</t>
@@ -1449,10 +1465,8 @@
           <t>Njeri Kimani</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>254710807679</t>
-        </is>
+      <c r="D22" t="n">
+        <v>254710807679</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -1462,7 +1476,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Beth Wambui Kihiko</t>
@@ -1496,10 +1514,8 @@
           <t>Wambui Matu</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>254715155936</t>
-        </is>
+      <c r="D23" t="n">
+        <v>254715155936</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1509,7 +1525,11 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Wambui Beth Wangari</t>
@@ -1531,22 +1551,20 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21791345</v>
+        <v>39262726</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Tabitha</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wanjiku Nyaguthii (REPEAT)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>254716872853</t>
-        </is>
+          <t>Wangari Ndiro</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>254794080835</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1556,12 +1574,22 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Esther Nyakiri Chege</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>254743958657</v>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1572,22 +1600,20 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39262726</v>
+        <v>5751111</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tabitha</t>
+          <t>Rahab</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wangari Ndiro</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>254794080835</t>
-        </is>
+          <t>Wanjiku Kimani</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>254704919175</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1597,14 +1623,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Esther Nyakiri Chege</t>
+          <t>Simon Nganga Kariuki</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>254743958657</v>
+        <v>254712731304</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1619,22 +1649,20 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5751111</v>
+        <v>24034006</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rahab</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wanjiku Kimani</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>254704919175</t>
-        </is>
+          <t>Nyambura Mugekenyi</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>254113017122</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1644,14 +1672,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Simon Nganga Kariuki</t>
+          <t>Esther Muthoni Mwaura</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>254712731304</v>
+        <v>254704888492</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1666,22 +1698,20 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24034006</v>
+        <v>28599488</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Evalyne</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nyambura Mugekenyi</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>254113017122</t>
-        </is>
+          <t>Wanjiru Gichuhi</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>254727633627</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -1691,14 +1721,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Esther Muthoni Mwaura</t>
+          <t>Mary Wangari Mwangi</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>254704888492</v>
+        <v>254115931777</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1713,22 +1747,20 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28599488</v>
+        <v>13212667</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Evalyne</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wanjiru Gichuhi</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>254727633627</t>
-        </is>
+          <t>Mathenge Wachira</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>254743201965</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
@@ -1738,14 +1770,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Mary Wangari Mwangi</t>
+          <t>Paul Ng'ang'a Gichuhi</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>254115931777</v>
+        <v>254712089478</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1760,22 +1796,20 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13212667</v>
+        <v>12417467</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mathenge Wachira</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>254743201965</t>
-        </is>
+          <t>Ruhangi Mwangi</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>254722610107</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -1785,14 +1819,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Paul Ng'ang'a Gichuhi</t>
+          <t>John Kimani Ngotho</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>254712089478</v>
+        <v>254721156069</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1807,22 +1845,20 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>12417467</v>
+        <v>26903488</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Teresiah</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ruhangi Mwangi</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>254722610107</t>
-        </is>
+          <t>Nduta Gitau</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>254717160355</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1832,14 +1868,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>John Kimani Ngotho</t>
+          <t>Kennedy Kirumba Gitau</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>254721156069</v>
+        <v>254114975258</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1854,22 +1894,20 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>26903488</v>
+        <v>22372303</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Teresiah</t>
+          <t>John</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nduta Gitau</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>254717160355</t>
-        </is>
+          <t>Mirara Muthoga</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>254720141895</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1879,14 +1917,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Kennedy Kirumba Gitau</t>
+          <t>Patrick Njoroge Kungu</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>254114975258</v>
+        <v>254745078949</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1901,22 +1943,20 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>22372303</v>
+        <v>24938672</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mirara Muthoga</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>254720141895</t>
-        </is>
+          <t>Nyaguthii</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>254716838439</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1926,14 +1966,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Patrick Njoroge Kungu</t>
+          <t>Mirriam Wairimu Gitaka</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>254745078949</v>
+        <v>254741123659</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1948,43 +1992,43 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>24938672</v>
+        <v>27492006</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Mercy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nyaguthii</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>254716838439</t>
-        </is>
+          <t>Nyambura Maina</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>254705110957</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Karatina</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Mirriam Wairimu Gitaka</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>254741123659</v>
-      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Dormant</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -1995,41 +2039,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>27492006</v>
+        <v>26869225</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mercy</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nyambura Maina</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>254705110957</t>
-        </is>
+          <t>Njambi Numera</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>254720323442</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Karatina</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Mary Wanjiku Muigai</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>254715641477</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Dormant</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2040,22 +2088,20 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>26869225</v>
+        <v>27860175</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Njambi Numera</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>254720323442</t>
-        </is>
+          <t>Nyambura Gitau</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>254716589853</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -2065,14 +2111,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Mary Wanjiku Muigai</t>
+          <t>Esther Wanjiru Muriithi</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>254715641477</v>
+        <v>254111573126</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2087,22 +2137,20 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>27860175</v>
+        <v>26744903</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Fredrick</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nyambura Gitau</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>254716589853</t>
-        </is>
+          <t>Odionyi</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>254723294698</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -2112,14 +2160,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Esther Wanjiru Muriithi</t>
+          <t>Dorcas Wambui Kamau</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>254111573126</v>
+        <v>254718958835</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2134,22 +2186,20 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>26744903</v>
+        <v>28382916</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fredrick</t>
+          <t>Salome</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Odionyi</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>254723294698</t>
-        </is>
+          <t>Njeri Mbuthia</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>254710359610</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -2159,14 +2209,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Dorcas Wambui Kamau</t>
+          <t>Mary Njeri Kamau</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>254718958835</v>
+        <v>254716427700</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2181,22 +2235,20 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>28382916</v>
+        <v>28102915</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salome</t>
+          <t>Naomi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Njeri Mbuthia</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>254710359610</t>
-        </is>
+          <t>Wanjiru Njuguna</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>254701890277</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -2206,14 +2258,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Mary Njeri Kamau</t>
+          <t>Grace Wambui Kirungo</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>254716427700</v>
+        <v>254748838165</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2228,22 +2284,20 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>28102915</v>
+        <v>33003036</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Naomi</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wanjiru Njuguna</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>254701890277</t>
-        </is>
+          <t>Njogu Ndekei</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>254758457833</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -2253,14 +2307,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Grace Wambui Kirungo</t>
+          <t>Benson Muthee Kinyanjui</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>254748838165</v>
+        <v>254114361766</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2275,22 +2333,20 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>33003036</v>
+        <v>25476433</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Njogu Ndekei</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>254758457833</t>
-        </is>
+          <t>Gathoni Chege</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>254724706953</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -2300,14 +2356,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Benson Muthee Kinyanjui</t>
+          <t>Josphine Njoki Ndung'u</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>254114361766</v>
+        <v>254725569996</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2322,22 +2382,20 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>25476433</v>
+        <v>7028707</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gathoni Chege</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>254724706953</t>
-        </is>
+          <t>Wachuka Kariuki</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>254722572202</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -2347,14 +2405,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Josphine Njoki Ndung'u</t>
+          <t>Jackline Warukira Kariuki</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>254725569996</v>
+        <v>254702695058</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2369,22 +2431,20 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7028707</v>
+        <v>25486582</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wachuka Kariuki</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>254722572202</t>
-        </is>
+          <t>Wanjiku Macharia</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>254721307339</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -2394,14 +2454,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Jackline Warukira Kariuki</t>
+          <t>Peter Karibu Githitu</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>254702695058</v>
+        <v>254701640618</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2416,22 +2480,20 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>25486582</v>
+        <v>31012591</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Damaris</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wanjiku Macharia</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>254721307339</t>
-        </is>
+          <t>Wairimu Mwangi</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>254791508489</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -2441,14 +2503,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Peter Karibu Githitu</t>
+          <t>Grace Wanjiru Karungo</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>254701640618</v>
+        <v>254727903371</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2463,22 +2529,20 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>31012591</v>
+        <v>32517912</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Damaris</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wairimu Mwangi</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>254791508489</t>
-        </is>
+          <t>Mugure Macharia</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>254116606404</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -2488,14 +2552,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Grace Wanjiru Karungo</t>
+          <t>Grace Wambui Ndiritu</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>254727903371</v>
+        <v>254115444106</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2510,22 +2578,20 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>32517912</v>
+        <v>22118116</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mugure Macharia</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>254116606404</t>
-        </is>
+          <t>Mwangi Kirima</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>254791724230</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -2535,14 +2601,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Grace Wambui Ndiritu</t>
+          <t>Paul Thiong'o Mwangi</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>254115444106</v>
+        <v>254717034868</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2557,22 +2627,20 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>22118116</v>
+        <v>26275607</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Tabitha</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mwangi Kirima</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>254791724230</t>
-        </is>
+          <t>Wangari Kimani</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>254715484117</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -2582,14 +2650,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Paul Thiong'o Mwangi</t>
+          <t>Juliana Nyokabi Njogu</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>254717034868</v>
+        <v>254704296513</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2604,22 +2676,20 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>26275607</v>
+        <v>25532121</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tabitha</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wangari Kimani</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>254715484117</t>
-        </is>
+          <t>Wanjiru</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>254706815518</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -2629,14 +2699,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Juliana Nyokabi Njogu</t>
+          <t>Ruth Wairimu Ngatia</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>254704296513</v>
+        <v>254721320807</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2651,22 +2725,20 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25532121</v>
+        <v>36160319</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Ann</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>254706815518</t>
-        </is>
+          <t>Njoki Njanja</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>254798733681</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -2676,14 +2748,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ruth Wairimu Ngatia</t>
+          <t>Mercy Murugi Mutundu</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>254721320807</v>
+        <v>254707405265</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2698,22 +2774,20 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>32739955</v>
+        <v>9815102</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mose</t>
+          <t>Leah</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bahati Bevlyne(Repeat)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>254711670920</t>
-        </is>
+          <t>Wanjiru Waweru</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>254142165052</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2723,12 +2797,22 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Hannah Nyokabi Kungu</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>254715007156</v>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -2739,22 +2823,20 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>36160319</v>
+        <v>21905797</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ann</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Njoki Njanja</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>254798733681</t>
-        </is>
+          <t>Maina Mworia</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>254703560538</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -2764,14 +2846,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Mercy Murugi Mutundu</t>
+          <t>David Maina Wambui</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>254707405265</v>
+        <v>254758411395</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2786,22 +2872,20 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>42233463</v>
+        <v>8060028</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Njeri Wanjiku (repeat)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>254119675041</t>
-        </is>
+          <t>Wambui Nguku</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>254798258604</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -2811,12 +2895,22 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Andrew Mungai Thuo</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>254706106746</v>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -2827,22 +2921,20 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25467679</v>
+        <v>24633265</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Priscillah</t>
+          <t>Sera</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nyambura Mutonya (REPEAT)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>254715885492</t>
-        </is>
+          <t>Muringa Ruoro</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>254740897616</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -2852,14 +2944,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>HORIZON044</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Hannah Wairimu Githinji</t>
+          <t>Obadiah Mburu Ruoro</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>254707572433</v>
+        <v>254712477429</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2874,22 +2970,20 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>32798367</v>
+        <v>27307693</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abigael</t>
+          <t>Beatrice</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gichemba Noah (REPEAT)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>254746130036</t>
-        </is>
+          <t>Nyambura Mwangi</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>254726601789</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
@@ -2899,14 +2993,18 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>HORIZON043</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>John Kanini Nyaga</t>
+          <t>Esther Wambui Wachira</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>254702014098</v>
+        <v>254727118382</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2914,241 +3012,6 @@
         </is>
       </c>
       <c r="M53" t="inlineStr">
-        <is>
-          <t>Migrated from Engineer branch loans</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>9815102</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Leah</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Wanjiru Waweru</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>254142165052</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Hannah Nyokabi Kungu</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>254715007156</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Migrated from Engineer branch loans</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>21905797</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Maina Mworia</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>254703560538</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>David Maina Wambui</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>254758411395</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Migrated from Engineer branch loans</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>8060028</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Wambui Nguku</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>254798258604</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Andrew Mungai Thuo</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>254706106746</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Migrated from Engineer branch loans</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>24633265</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Sera</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Muringa Ruoro</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>254740897616</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Obadiah Mburu Ruoro</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>254712477429</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Migrated from Engineer branch loans</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>27307693</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Beatrice</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nyambura Mwangi</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>254726601789</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Esther Wambui Wachira</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>254727118382</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
         <is>
           <t>Migrated from Engineer branch loans</t>
         </is>
